--- a/employee_surveys/016_workplace_safety_and_concerns_form--employee_surveys.xlsx
+++ b/employee_surveys/016_workplace_safety_and_concerns_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
